--- a/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/test4/INVENTORY_BALANCES.xlsx
+++ b/sqlapp-command/src/test/resources/com/sqlapp/data/db/command/generator/test4/INVENTORY_BALANCES.xlsx
@@ -9,6 +9,7 @@
     <sheet name="Table" r:id="rId3" sheetId="1"/>
     <sheet name="Column" r:id="rId4" sheetId="2"/>
     <sheet name="Query" r:id="rId5" sheetId="3"/>
+    <sheet name="File" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
@@ -83,17 +84,72 @@
     </comment>
     <comment ref="C1" authorId="0">
       <text>
-        <t>offset for SELECT SQL.</t>
+        <t>This is an MVEL expression that creates a map that maps columns in the data source to columns in the table.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
-        <t>limit for SELECT SQL.</t>
+        <t>offset for SELECT SQL.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0">
       <text>
+        <t>limit for SELECT SQL.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
         <t>NEXT_VALUE OR RANDOM</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <t>Specify the weighting for random data selection using the MVEL formula. By default, the weight for each row is 1.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <t>If the name given here is set to the group name of the column sheet, the results of the SELECT SQL will be used.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <t>This is an MVEL expression that reads data sources such as files and returns an iterable of Map objects.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <t>This is an MVEL expression that creates a map that maps columns in the data source to columns in the table.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <t>offset for SELECT SQL.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0">
+      <text>
+        <t>limit for SELECT SQL.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <t>NEXT_VALUE OR RANDOM</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <t>Specify the weighting for random data selection using the MVEL formula. By default, the weight for each row is 1.</t>
       </text>
     </comment>
   </commentList>
@@ -101,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="45">
   <si>
     <t>Table Name</t>
   </si>
@@ -145,13 +201,13 @@
 	, /*PRODUCT_ID*/0
 	, /*QUANTITY*/0
 FROM (VALUES(0))
-WHERE
-NOT EXISTS (
+WHERE NOT EXISTS
+(
 	SELECT 1
 	FROM INVENTORY_BALANCES
 	WHERE 1=1
-	AND WAREHOUSE_ID = /*WAREHOUSE_ID*/0
-	AND PRODUCT_ID = /*PRODUCT_ID*/0
+		AND WAREHOUSE_ID = /*WAREHOUSE_ID*/0
+		AND PRODUCT_ID = /*PRODUCT_ID*/0
 )
 </t>
   </si>
@@ -216,6 +272,9 @@
     <t>Select SQL</t>
   </si>
   <si>
+    <t>Column Mapping Expression</t>
+  </si>
+  <si>
     <t>Offset</t>
   </si>
   <si>
@@ -223,6 +282,9 @@
   </si>
   <si>
     <t>Selection Strategy</t>
+  </si>
+  <si>
+    <t>Selection Strategy weight expression</t>
   </si>
   <si>
     <t>Group1</t>
@@ -249,6 +311,25 @@
     <t>SELECT
 	WAREHOUSE_ID
 FROM PUBLIC.WAREHOUSES</t>
+  </si>
+  <si>
+    <t>DataSource Expression</t>
+  </si>
+  <si>
+    <t>FileGroup1</t>
+  </si>
+  <si>
+    <t>[
+	["a":"1", "b":2]
+	,["a":"3", "b":4]
+]</t>
+  </si>
+  <si>
+    <t>[
+"col_a":a
+,"col_b":b
+,"col_c":"cccc"
+]</t>
   </si>
 </sst>
 </file>
@@ -256,13 +337,189 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="361">
+  <fonts count="405">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -1763,7 +2020,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="181">
+  <cellXfs count="203">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment horizontal="left" vertical="center"/>
@@ -2260,11 +2517,11 @@
     <xf numFmtId="0" fontId="330" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="332" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment vertical="center" wrapText="true"/>
-    </xf>
-    <xf numFmtId="0" fontId="334" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
-      <alignment vertical="center" wrapText="true"/>
+    <xf numFmtId="0" fontId="332" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="334" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="336" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="center" wrapText="true"/>
@@ -2303,6 +2560,72 @@
       <alignment vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="360" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="362" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="364" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="366" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="368" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="370" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="372" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="374" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="376" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="378" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="380" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="382" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="384" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="386" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="388" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="390" fillId="3" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="392" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="394" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="396" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="398" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="400" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="402" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="404" fillId="5" borderId="4" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -2318,6 +2641,10 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
 </file>
 
@@ -2605,14 +2932,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="34.22265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="24.09375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="5.85546875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="10.9296875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="15.390625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.73828125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="5.85546875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="10.9296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="15.390625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="30.3671875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2631,57 +2960,134 @@
       <c r="E1" s="165" t="s">
         <v>32</v>
       </c>
+      <c r="F1" s="166" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="167" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="2" ht="75.0" customHeight="true">
-      <c r="A2" s="166" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="167" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="168" t="n">
+      <c r="A2" s="168" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="169" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" s="170"/>
+      <c r="D2" s="171" t="n">
         <v>0.0</v>
       </c>
-      <c r="D2" s="169" t="n">
+      <c r="E2" s="172" t="n">
         <v>2.147483647E9</v>
       </c>
-      <c r="E2" s="170" t="s">
-        <v>35</v>
-      </c>
+      <c r="F2" s="173" t="s">
+        <v>37</v>
+      </c>
+      <c r="G2" s="174"/>
     </row>
     <row r="3" ht="45.0" customHeight="true">
-      <c r="A3" s="171" t="s">
+      <c r="A3" s="175" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="172" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="173" t="n">
+      <c r="B3" s="176" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="177"/>
+      <c r="D3" s="178" t="n">
         <v>0.0</v>
       </c>
-      <c r="D3" s="174" t="n">
+      <c r="E3" s="179" t="n">
         <v>2.147483647E9</v>
       </c>
-      <c r="E3" s="175" t="s">
-        <v>37</v>
-      </c>
+      <c r="F3" s="180" t="s">
+        <v>39</v>
+      </c>
+      <c r="G3" s="181"/>
     </row>
     <row r="4" ht="45.0" customHeight="true">
-      <c r="A4" s="176" t="s">
+      <c r="A4" s="182" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="177" t="s">
-        <v>38</v>
-      </c>
-      <c r="C4" s="178" t="n">
+      <c r="B4" s="183" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="184"/>
+      <c r="D4" s="185" t="n">
         <v>0.0</v>
       </c>
-      <c r="D4" s="179" t="n">
+      <c r="E4" s="186" t="n">
         <v>2.147483647E9</v>
       </c>
-      <c r="E4" s="180" t="s">
+      <c r="F4" s="187" t="s">
+        <v>39</v>
+      </c>
+      <c r="G4" s="188"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="15.4921875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="19.2265625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.73828125" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="5.85546875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="10.9296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="15.390625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="30.3671875" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="189" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="190" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="191" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="192" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" s="193" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="194" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="195" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" ht="75.0" customHeight="true">
+      <c r="A2" s="196" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="197" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="198" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="199" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="E2" s="200" t="n">
+        <v>2.147483647E9</v>
+      </c>
+      <c r="F2" s="201" t="s">
         <v>37</v>
       </c>
+      <c r="G2" s="202"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
